--- a/jira_export_2026-07-06.xlsx
+++ b/jira_export_2026-07-06.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>123 h</t>
+          <t>128 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P135"/>
+  <dimension ref="A1:P137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -957,7 +957,7 @@
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
@@ -1182,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L6" s="15" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>1</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L16" s="15" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>4</v>
       </c>
       <c r="K66" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L66" s="15" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>4</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
@@ -6663,32 +6663,32 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6698,34 +6698,34 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>130</v>
-      </c>
-      <c r="O83" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P83" s="13" t="n">
@@ -6735,12 +6735,12 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
@@ -6786,16 +6786,16 @@
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O84" s="17" t="n">
         <v>0</v>
@@ -6807,12 +6807,12 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
@@ -6847,27 +6847,27 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>1000</v>
+        <v>255</v>
       </c>
       <c r="O85" s="17" t="n">
         <v>0</v>
@@ -6879,12 +6879,12 @@
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J86" s="15" t="n">
@@ -6930,16 +6930,16 @@
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="O86" s="17" t="n">
         <v>0</v>
@@ -6951,27 +6951,27 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
@@ -7002,16 +7002,16 @@
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="O87" s="17" t="n">
         <v>0</v>
@@ -7023,32 +7023,32 @@
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G88" s="15" t="inlineStr">
@@ -7058,34 +7058,34 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="16" t="n">
+        <v>200</v>
+      </c>
+      <c r="O88" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="16" t="n">
@@ -7095,12 +7095,12 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
@@ -7146,18 +7146,18 @@
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>350</v>
-      </c>
-      <c r="O89" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="13" t="n">
@@ -7167,27 +7167,27 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
@@ -7207,29 +7207,29 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>3.75</v>
+        <v>0.75</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="O90" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="16" t="n">
@@ -7239,12 +7239,12 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -7279,23 +7279,23 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>0.25</v>
+        <v>3.75</v>
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
@@ -7455,26 +7455,28 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
@@ -7493,29 +7495,29 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O94" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P94" s="16" t="n">
@@ -7525,12 +7527,12 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
@@ -7540,7 +7542,7 @@
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
         </is>
       </c>
       <c r="E95" s="12" t="n">
@@ -7558,32 +7560,32 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>2812.32</v>
+        <v>157.5</v>
       </c>
       <c r="O95" s="17" t="n">
         <v>0</v>
@@ -7595,12 +7597,12 @@
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7610,13 +7612,11 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v/>
       </c>
       <c r="F96" s="15" t="inlineStr">
         <is>
@@ -7635,27 +7635,27 @@
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>392.5</v>
+        <v>2812.32</v>
       </c>
       <c r="O96" s="17" t="n">
         <v>0</v>
@@ -7718,16 +7718,16 @@
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>1556.25</v>
+        <v>392.5</v>
       </c>
       <c r="O97" s="17" t="n">
         <v>0</v>
@@ -7790,16 +7790,16 @@
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M98" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N98" s="16" t="n">
-        <v>1790</v>
+        <v>1556.25</v>
       </c>
       <c r="O98" s="17" t="n">
         <v>0</v>
@@ -7862,18 +7862,18 @@
       </c>
       <c r="L99" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M99" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N99" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="13" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O99" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="13" t="n">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
@@ -7955,12 +7955,12 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
@@ -7970,11 +7970,13 @@
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
@@ -7988,28 +7990,28 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
@@ -8025,12 +8027,12 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -8040,7 +8042,7 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E102" s="15" t="n">
@@ -8058,34 +8060,34 @@
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J102" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="O102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8095,28 +8097,26 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v/>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
@@ -8135,29 +8135,29 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="13" t="n">
+        <v>732</v>
+      </c>
+      <c r="O103" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="13" t="n">
@@ -8167,26 +8167,28 @@
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
@@ -8205,29 +8207,29 @@
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
@@ -8237,12 +8239,12 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -8252,7 +8254,7 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E105" s="12" t="n">
@@ -8270,34 +8272,34 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="13" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O105" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="13" t="n">
@@ -8307,22 +8309,22 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E106" s="15" t="n">
@@ -8345,23 +8347,23 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
@@ -8377,12 +8379,12 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -8392,7 +8394,7 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E107" s="12" t="n">
@@ -8410,28 +8412,28 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>1.38</v>
+        <v>0.25</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
@@ -8496,12 +8498,12 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
@@ -8517,22 +8519,22 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E109" s="12" t="n">
@@ -8555,29 +8557,29 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O109" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
@@ -8587,22 +8589,22 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8610,7 +8612,7 @@
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G110" s="15" t="inlineStr">
@@ -8620,32 +8622,32 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>964.1</v>
+        <v>2323</v>
       </c>
       <c r="O110" s="17" t="n">
         <v>0</v>
@@ -8657,12 +8659,12 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
@@ -8706,19 +8708,19 @@
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
-        <v>140.4</v>
+        <v>964.1</v>
       </c>
       <c r="O111" s="17" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
         <v>0</v>
@@ -8727,17 +8729,17 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
@@ -8750,7 +8752,7 @@
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G112" s="15" t="inlineStr">
@@ -8765,30 +8767,30 @@
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O112" s="16" t="n">
-        <v>0</v>
+        <v>140.4</v>
+      </c>
+      <c r="O112" s="17" t="n">
+        <v>70.2</v>
       </c>
       <c r="P112" s="16" t="n">
         <v>0</v>
@@ -8797,22 +8799,22 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
@@ -8820,7 +8822,7 @@
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -8835,29 +8837,29 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O113" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="13" t="n">
@@ -8867,22 +8869,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8890,7 +8892,7 @@
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G114" s="15" t="inlineStr">
@@ -8900,34 +8902,34 @@
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O114" s="16" t="n">
+        <v>482.72</v>
+      </c>
+      <c r="O114" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
@@ -8937,22 +8939,22 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8970,34 +8972,34 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="O115" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P115" s="13" t="n">
@@ -9007,22 +9009,22 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
@@ -9045,27 +9047,27 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>460</v>
+        <v>250</v>
       </c>
       <c r="O116" s="17" t="n">
         <v>0</v>
@@ -9077,12 +9079,12 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
@@ -9092,7 +9094,7 @@
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
@@ -9115,29 +9117,29 @@
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="13" t="n">
+        <v>230</v>
+      </c>
+      <c r="O117" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="13" t="n">
@@ -9147,22 +9149,22 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9178,32 +9180,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H118" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H118" s="15" t="inlineStr"/>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L118" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27377</t>
-        </is>
-      </c>
-      <c r="M118" s="15" t="inlineStr">
-        <is>
-          <t>478048</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L118" s="15" t="inlineStr"/>
+      <c r="M118" s="15" t="inlineStr"/>
       <c r="N118" s="16" t="n">
         <v>0</v>
       </c>
@@ -9217,12 +9207,12 @@
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
@@ -9232,7 +9222,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9250,28 +9240,28 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J119" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K119" s="12" t="n">
         <v>0.25</v>
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9287,12 +9277,12 @@
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
@@ -9302,7 +9292,7 @@
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -9315,7 +9305,7 @@
       </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H120" s="15" t="inlineStr">
@@ -9325,17 +9315,25 @@
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L120" s="15" t="inlineStr"/>
-      <c r="M120" s="15" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L120" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M120" s="15" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N120" s="16" t="n">
         <v>0</v>
       </c>
@@ -9349,22 +9347,22 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9372,7 +9370,7 @@
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -9382,34 +9380,34 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="13" t="n">
@@ -9419,12 +9417,12 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
@@ -9434,7 +9432,7 @@
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9447,35 +9445,27 @@
       </c>
       <c r="G122" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L122" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34362</t>
-        </is>
-      </c>
-      <c r="M122" s="15" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L122" s="15" t="inlineStr"/>
+      <c r="M122" s="15" t="inlineStr"/>
       <c r="N122" s="16" t="n">
         <v>0</v>
       </c>
@@ -9489,22 +9479,22 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9512,7 +9502,7 @@
       </c>
       <c r="F123" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
@@ -9522,34 +9512,34 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O123" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="13" t="n">
@@ -9559,22 +9549,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9582,32 +9572,40 @@
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G124" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H124" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K124" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L124" s="15" t="inlineStr"/>
-      <c r="M124" s="15" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="L124" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M124" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N124" s="16" t="n">
         <v>0</v>
       </c>
@@ -9621,22 +9619,22 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9649,7 +9647,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
@@ -9659,17 +9657,25 @@
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L125" s="12" t="inlineStr"/>
-      <c r="M125" s="12" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="L125" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M125" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N125" s="13" t="n">
         <v>0</v>
       </c>
@@ -9683,22 +9689,22 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9706,7 +9712,7 @@
       </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G126" s="15" t="inlineStr">
@@ -9716,19 +9722,19 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="L126" s="15" t="inlineStr"/>
       <c r="M126" s="15" t="inlineStr"/>
@@ -9745,22 +9751,22 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9783,14 +9789,14 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L127" s="12" t="inlineStr"/>
       <c r="M127" s="12" t="inlineStr"/>
@@ -9807,22 +9813,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9840,19 +9846,19 @@
       </c>
       <c r="H128" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L128" s="15" t="inlineStr"/>
       <c r="M128" s="15" t="inlineStr"/>
@@ -9869,12 +9875,12 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -9884,7 +9890,7 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9897,7 +9903,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H129" s="12" t="inlineStr">
@@ -9907,25 +9913,17 @@
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L129" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M129" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr"/>
+      <c r="M129" s="12" t="inlineStr"/>
       <c r="N129" s="13" t="n">
         <v>0</v>
       </c>
@@ -9939,28 +9937,26 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E130" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CC du Pays Sabolien</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v/>
       </c>
       <c r="F130" s="15" t="inlineStr">
         <is>
@@ -9979,14 +9975,14 @@
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L130" s="15" t="inlineStr"/>
       <c r="M130" s="15" t="inlineStr"/>
@@ -10003,12 +9999,12 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
@@ -10018,13 +10014,11 @@
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="n">
+        <v/>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
@@ -10033,7 +10027,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H131" s="12" t="inlineStr">
@@ -10043,17 +10037,25 @@
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L131" s="12" t="inlineStr"/>
-      <c r="M131" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N131" s="13" t="n">
         <v>0</v>
       </c>
@@ -10067,23 +10069,27 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C132" s="15" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C132" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E132" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F132" s="15" t="inlineStr">
@@ -10103,14 +10109,14 @@
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="L132" s="15" t="inlineStr"/>
       <c r="M132" s="15" t="inlineStr"/>
@@ -10127,21 +10133,29 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C133" s="12" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E133" s="12" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10149,35 +10163,31 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H133" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M133" s="12" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L133" s="12" t="inlineStr"/>
+      <c r="M133" s="12" t="inlineStr"/>
       <c r="N133" s="13" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O133" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="13" t="n">
@@ -10187,89 +10197,209 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr"/>
       <c r="D134" s="15" t="inlineStr">
         <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E134" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F134" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G134" s="15" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H134" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I134" s="15" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J134" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="K134" s="15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L134" s="15" t="inlineStr"/>
+      <c r="M134" s="15" t="inlineStr"/>
+      <c r="N134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr"/>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr"/>
+      <c r="F135" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H135" s="12" t="inlineStr"/>
+      <c r="I135" s="12" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J135" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M135" s="12" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N135" s="13" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O135" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1228</t>
+        </is>
+      </c>
+      <c r="B136" s="15" t="inlineStr">
+        <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E134" s="15" t="inlineStr"/>
-      <c r="F134" s="15" t="inlineStr">
+      <c r="C136" s="15" t="inlineStr"/>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MERLEVENEZ</t>
+        </is>
+      </c>
+      <c r="E136" s="15" t="inlineStr"/>
+      <c r="F136" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G134" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H134" s="15" t="inlineStr"/>
-      <c r="I134" s="15" t="inlineStr">
+      <c r="G136" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H136" s="15" t="inlineStr"/>
+      <c r="I136" s="15" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J134" s="15" t="n">
+      <c r="J136" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="K134" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="15" t="inlineStr">
+      <c r="K136" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M134" s="15" t="inlineStr">
+      <c r="M136" s="15" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N134" s="16" t="n">
+      <c r="N136" s="16" t="n">
         <v>50</v>
       </c>
-      <c r="O134" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" s="16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="18" t="inlineStr">
+      <c r="O136" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B135" s="18" t="inlineStr"/>
-      <c r="C135" s="18" t="inlineStr"/>
-      <c r="D135" s="18" t="inlineStr"/>
-      <c r="E135" s="18" t="inlineStr"/>
-      <c r="F135" s="18" t="inlineStr"/>
-      <c r="G135" s="18" t="inlineStr"/>
-      <c r="H135" s="18" t="inlineStr"/>
-      <c r="I135" s="18" t="inlineStr"/>
-      <c r="J135" s="18" t="inlineStr"/>
-      <c r="K135" s="18" t="inlineStr"/>
-      <c r="L135" s="18" t="inlineStr"/>
-      <c r="M135" s="18" t="inlineStr"/>
-      <c r="N135" s="19" t="n">
-        <v>68700.26000000001</v>
-      </c>
-      <c r="O135" s="19" t="n">
+      <c r="B137" s="18" t="inlineStr"/>
+      <c r="C137" s="18" t="inlineStr"/>
+      <c r="D137" s="18" t="inlineStr"/>
+      <c r="E137" s="18" t="inlineStr"/>
+      <c r="F137" s="18" t="inlineStr"/>
+      <c r="G137" s="18" t="inlineStr"/>
+      <c r="H137" s="18" t="inlineStr"/>
+      <c r="I137" s="18" t="inlineStr"/>
+      <c r="J137" s="18" t="inlineStr"/>
+      <c r="K137" s="18" t="inlineStr"/>
+      <c r="L137" s="18" t="inlineStr"/>
+      <c r="M137" s="18" t="inlineStr"/>
+      <c r="N137" s="19" t="n">
+        <v>68470.26000000001</v>
+      </c>
+      <c r="O137" s="19" t="n">
         <v>10055.38</v>
       </c>
-      <c r="P135" s="19" t="n">
-        <v>126.48</v>
+      <c r="P137" s="19" t="n">
+        <v>121.52</v>
       </c>
     </row>
   </sheetData>
@@ -10405,6 +10535,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId132"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10979,7 +11111,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>45.25</v>
+        <v>46.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>13.25</v>
@@ -10988,17 +11120,17 @@
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>59.25</v>
+        <v>60.75</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>13.75</v>
+        <v>14.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11141,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>17.75</v>
+        <v>19.5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>2.5</v>
@@ -11018,7 +11150,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>20.25</v>
+        <v>22</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>4</v>
@@ -11028,7 +11160,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
     </row>
@@ -11040,7 +11172,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>24.5</v>
+        <v>24.75</v>
       </c>
     </row>
   </sheetData>
@@ -11125,22 +11257,22 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>408978</v>
+        <v>402048</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>204262</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>204715</v>
+        <v>197785</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>169136</v>
+        <v>165176</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>17470</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>18109</v>
+        <v>15139</v>
       </c>
     </row>
     <row r="6">
@@ -11175,22 +11307,22 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>223059</v>
+        <v>216129</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>123477</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>99582</v>
+        <v>92652</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>72761</v>
+        <v>68801</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>12700</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>14121</v>
+        <v>11151</v>
       </c>
     </row>
   </sheetData>
